--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_357_R36.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_357_R36.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.4547</v>
+        <v>6.2022</v>
       </c>
       <c r="E2" t="n">
-        <v>6.1529</v>
+        <v>6.4635</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.6982</v>
+        <v>-0.2613</v>
       </c>
       <c r="G2" t="n">
         <v>7.56</v>
@@ -610,13 +610,13 @@
         <v>1.3917</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.5564</v>
+        <v>-0.8090000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.963</v>
+        <v>-0.6524</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5935</v>
+        <v>-0.1566</v>
       </c>
       <c r="V2" t="n">
         <v>2.0026</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.0814</v>
+        <v>2.7749</v>
       </c>
       <c r="E3" t="n">
-        <v>2.7109</v>
+        <v>1.606</v>
       </c>
       <c r="F3" t="n">
-        <v>1.3705</v>
+        <v>1.1689</v>
       </c>
       <c r="G3" t="n">
         <v>3.5071</v>
@@ -688,13 +688,13 @@
         <v>1.1598</v>
       </c>
       <c r="S3" t="n">
-        <v>2.8062</v>
+        <v>1.4998</v>
       </c>
       <c r="T3" t="n">
-        <v>2.2413</v>
+        <v>1.1365</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5649</v>
+        <v>0.3633</v>
       </c>
       <c r="V3" t="n">
         <v>-1.0722</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4206</v>
+        <v>1.3944</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7704</v>
+        <v>0.845</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6502</v>
+        <v>0.5494</v>
       </c>
       <c r="G4" t="n">
         <v>0.1221</v>
@@ -766,13 +766,13 @@
         <v>1.8556</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6954</v>
+        <v>0.6693</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2205</v>
+        <v>0.2952</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4749</v>
+        <v>0.3741</v>
       </c>
       <c r="V4" t="n">
         <v>-0.7886</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. DIOUF</t>
+          <t>M. BAIOCCHI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7288</v>
+        <v>0.1573</v>
       </c>
       <c r="E5" t="n">
-        <v>2.2701</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.5414</v>
+        <v>0.1573</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.0424</v>
+        <v>0.1573</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.1358</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.9067</v>
+        <v>0.1573</v>
       </c>
       <c r="J5" t="n">
-        <v>1.3459</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0945</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>1.2514</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-3.3883</v>
+        <v>0.1573</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.2303</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.1581</v>
+        <v>0.1573</v>
       </c>
       <c r="P5" t="n">
-        <v>1.1598</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.4639</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.6237</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1.7532</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>1.3882</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3651</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1769</v>
+        <v>-0.1598</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3609</v>
+        <v>-0.5968</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5377999999999999</v>
+        <v>0.4369</v>
       </c>
       <c r="G6" t="n">
         <v>-0.1451</v>
@@ -922,13 +922,13 @@
         <v>0.4639</v>
       </c>
       <c r="S6" t="n">
-        <v>1.0179</v>
+        <v>0.6811</v>
       </c>
       <c r="T6" t="n">
-        <v>0.7117</v>
+        <v>0.4758</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3062</v>
+        <v>0.2054</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. BAIOCCHI</t>
+          <t>K. JALLOW</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1573</v>
+        <v>-0.3991</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>0.2661</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1573</v>
+        <v>-0.6651</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1573</v>
+        <v>-0.9546</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>-0.533</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1573</v>
+        <v>-0.4216</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>0.8437</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>0.8437</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1573</v>
+        <v>-1.7983</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>-1.3767</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1573</v>
+        <v>-0.4216</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-0.232</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>0.9278</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>0.7874</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>0.5821</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>0.2054</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. SMAILAGIC</t>
+          <t>M. DIOUF</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3552</v>
+        <v>-0.4336</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1568</v>
+        <v>1.2086</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1983</v>
+        <v>-1.6422</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.744</v>
+        <v>-2.0424</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0457</v>
+        <v>-1.1358</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.7896</v>
+        <v>-0.9067</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0672</v>
+        <v>1.3459</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0672</v>
+        <v>0.0945</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.2514</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.8112</v>
+        <v>-3.3883</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0216</v>
+        <v>-1.2303</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.7896</v>
+        <v>-2.1581</v>
       </c>
       <c r="P8" t="n">
-        <v>0.4639</v>
+        <v>1.1598</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.4639</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4639</v>
+        <v>1.6237</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0751</v>
+        <v>0.5909</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.224</v>
+        <v>0.3266</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1489</v>
+        <v>0.2642</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>K. JALLOW</t>
+          <t>A. SMAILAGIC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.1404</v>
+        <v>-0.456</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.4417</v>
+        <v>-0.1568</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6987</v>
+        <v>-0.2992</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.9546</v>
+        <v>-0.744</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.533</v>
+        <v>0.0457</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4216</v>
+        <v>-0.7896</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8437</v>
+        <v>0.0672</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8437</v>
+        <v>0.0672</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.7983</v>
+        <v>-0.8112</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.3767</v>
+        <v>-0.0216</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.4216</v>
+        <v>-0.7896</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.232</v>
+        <v>0.4639</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9278</v>
+        <v>0.4639</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0461</v>
+        <v>-0.1759</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1256</v>
+        <v>-0.224</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1718</v>
+        <v>0.0481</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.7519</v>
+        <v>-0.8179</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.4341</v>
+        <v>-2.5337</v>
       </c>
       <c r="F10" t="n">
-        <v>1.6822</v>
+        <v>1.7158</v>
       </c>
       <c r="G10" t="n">
         <v>0.09710000000000001</v>
@@ -1234,13 +1234,13 @@
         <v>0.6959</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2254</v>
+        <v>0.7086</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3576</v>
+        <v>0.5427</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1322</v>
+        <v>0.1658</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>F. FERRARI</t>
+          <t>D. ALSTON JR.</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.9085</v>
+        <v>-2.7051</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.4155</v>
+        <v>-2.3156</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.4929</v>
+        <v>-0.3895</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.3065</v>
+        <v>-4.8747</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.4189</v>
+        <v>-1.0001</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.8876</v>
+        <v>-3.8747</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.4551</v>
+        <v>-1.3898</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1176</v>
+        <v>0.4306</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.5727</v>
+        <v>-1.8204</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.8514</v>
+        <v>-3.4849</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.5365</v>
+        <v>-1.4306</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.3149</v>
+        <v>-2.0543</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.9278</v>
+        <v>0.9278</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1598</v>
+        <v>-1.6237</v>
       </c>
       <c r="R11" t="n">
-        <v>0.232</v>
+        <v>2.5515</v>
       </c>
       <c r="S11" t="n">
-        <v>1.3258</v>
+        <v>0.7057</v>
       </c>
       <c r="T11" t="n">
-        <v>1.1993</v>
+        <v>0.02</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1265</v>
+        <v>0.6858</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. ALSTON JR.</t>
+          <t>F. FERRARI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.3291</v>
+        <v>-3.8686</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.1413</v>
+        <v>-2.2412</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.1879</v>
+        <v>-1.6274</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.8747</v>
+        <v>-3.3065</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.0001</v>
+        <v>-0.4189</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.8747</v>
+        <v>-2.8876</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.3898</v>
+        <v>-1.4551</v>
       </c>
       <c r="K12" t="n">
-        <v>0.4306</v>
+        <v>0.1176</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.8204</v>
+        <v>-1.5727</v>
       </c>
       <c r="M12" t="n">
-        <v>-3.4849</v>
+        <v>-1.8514</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.4306</v>
+        <v>-0.5365</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.0543</v>
+        <v>-1.3149</v>
       </c>
       <c r="P12" t="n">
-        <v>0.9278</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.6237</v>
+        <v>-1.1598</v>
       </c>
       <c r="R12" t="n">
-        <v>2.5515</v>
+        <v>0.232</v>
       </c>
       <c r="S12" t="n">
-        <v>0.08169999999999999</v>
+        <v>0.3657</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8057</v>
+        <v>0.3736</v>
       </c>
       <c r="U12" t="n">
-        <v>0.8874</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="V12" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6778999999999999</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.676</v>
+        <v>-6.4567</v>
       </c>
       <c r="E13" t="n">
-        <v>-8.1031</v>
+        <v>-7.3207</v>
       </c>
       <c r="F13" t="n">
-        <v>0.427</v>
+        <v>0.8639</v>
       </c>
       <c r="G13" t="n">
         <v>-10.2956</v>
@@ -1468,13 +1468,13 @@
         <v>2.5515</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3651</v>
+        <v>0.8542</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.07820000000000001</v>
+        <v>0.7042</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2869</v>
+        <v>0.15</v>
       </c>
       <c r="V13" t="n">
         <v>3.2166</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-5.141399999999999</v>
+        <v>-4.767999999999998</v>
       </c>
       <c r="E14" t="n">
-        <v>-5.149100000000001</v>
+        <v>-4.7756</v>
       </c>
       <c r="F14" t="n">
-        <v>0.007599999999999718</v>
+        <v>0.007499999999999729</v>
       </c>
       <c r="G14" t="n">
         <v>-10.9193</v>
@@ -1516,13 +1516,13 @@
         <v>-6.4526</v>
       </c>
       <c r="I14" t="n">
-        <v>-4.466899999999999</v>
+        <v>-4.4669</v>
       </c>
       <c r="J14" t="n">
         <v>1.645800000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>0.2915999999999985</v>
+        <v>0.2915999999999994</v>
       </c>
       <c r="L14" t="n">
         <v>1.354099999999999</v>
@@ -1534,7 +1534,7 @@
         <v>-6.7441</v>
       </c>
       <c r="O14" t="n">
-        <v>-5.821099999999999</v>
+        <v>-5.8211</v>
       </c>
       <c r="P14" t="n">
         <v>-3.4795</v>
@@ -1546,13 +1546,13 @@
         <v>13.9173</v>
       </c>
       <c r="S14" t="n">
-        <v>5.5043</v>
+        <v>5.877800000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>3.2069</v>
+        <v>3.5803</v>
       </c>
       <c r="U14" t="n">
-        <v>2.2975</v>
+        <v>2.2976</v>
       </c>
       <c r="V14" t="n">
         <v>3.7527</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. MCCORMACK</t>
+          <t>N. DIMITRIJEVIC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.2223</v>
+        <v>3.7875</v>
       </c>
       <c r="E15" t="n">
-        <v>3.0638</v>
+        <v>2.6854</v>
       </c>
       <c r="F15" t="n">
-        <v>1.1584</v>
+        <v>1.1021</v>
       </c>
       <c r="G15" t="n">
-        <v>2.1272</v>
+        <v>5.6359</v>
       </c>
       <c r="H15" t="n">
-        <v>2.6156</v>
+        <v>3.133</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4884</v>
+        <v>2.5029</v>
       </c>
       <c r="J15" t="n">
-        <v>2.5776</v>
+        <v>5.6112</v>
       </c>
       <c r="K15" t="n">
-        <v>2.4304</v>
+        <v>3.7342</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1472</v>
+        <v>1.8771</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.4504</v>
+        <v>0.0246</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1852</v>
+        <v>-0.6012</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.6356000000000001</v>
+        <v>0.6258</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.232</v>
+        <v>-2.3195</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.5515</v>
+        <v>-3.7112</v>
       </c>
       <c r="R15" t="n">
-        <v>2.3195</v>
+        <v>1.3917</v>
       </c>
       <c r="S15" t="n">
-        <v>0.9713000000000001</v>
+        <v>-0.065</v>
       </c>
       <c r="T15" t="n">
-        <v>0.6097</v>
+        <v>-0.2869</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3616</v>
+        <v>0.2219</v>
       </c>
       <c r="V15" t="n">
-        <v>1.3558</v>
+        <v>0.5361</v>
       </c>
       <c r="W15" t="n">
-        <v>2.428</v>
+        <v>1.0722</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.0722</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>N. DIMITRIJEVIC</t>
+          <t>D. MCCORMACK</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.4615</v>
+        <v>3.4151</v>
       </c>
       <c r="E16" t="n">
-        <v>2.4495</v>
+        <v>2.3561</v>
       </c>
       <c r="F16" t="n">
-        <v>1.012</v>
+        <v>1.0589</v>
       </c>
       <c r="G16" t="n">
-        <v>5.6359</v>
+        <v>2.1272</v>
       </c>
       <c r="H16" t="n">
-        <v>3.133</v>
+        <v>2.6156</v>
       </c>
       <c r="I16" t="n">
-        <v>2.5029</v>
+        <v>-0.4884</v>
       </c>
       <c r="J16" t="n">
-        <v>5.6112</v>
+        <v>2.5776</v>
       </c>
       <c r="K16" t="n">
-        <v>3.7342</v>
+        <v>2.4304</v>
       </c>
       <c r="L16" t="n">
-        <v>1.8771</v>
+        <v>0.1472</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0246</v>
+        <v>-0.4504</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6012</v>
+        <v>0.1852</v>
       </c>
       <c r="O16" t="n">
-        <v>0.6258</v>
+        <v>-0.6356000000000001</v>
       </c>
       <c r="P16" t="n">
-        <v>-2.3195</v>
+        <v>-0.232</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.7112</v>
+        <v>-2.5515</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3917</v>
+        <v>2.3195</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.391</v>
+        <v>0.1641</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5228</v>
+        <v>-0.098</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1318</v>
+        <v>0.2621</v>
       </c>
       <c r="V16" t="n">
-        <v>0.5361</v>
+        <v>1.3558</v>
       </c>
       <c r="W16" t="n">
-        <v>1.0722</v>
+        <v>2.428</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.5361</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.2865</v>
+        <v>2.7247</v>
       </c>
       <c r="E17" t="n">
         <v>1.1691</v>
       </c>
       <c r="F17" t="n">
-        <v>1.1174</v>
+        <v>1.5556</v>
       </c>
       <c r="G17" t="n">
         <v>1.0666</v>
@@ -1780,13 +1780,13 @@
         <v>2.0876</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8676</v>
+        <v>-0.4294</v>
       </c>
       <c r="T17" t="n">
         <v>-0.2513</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.6163</v>
+        <v>-0.1781</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>I. MIKE</t>
+          <t>O. DA SILVA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.4206</v>
+        <v>1.8533</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.0384</v>
+        <v>0.3985</v>
       </c>
       <c r="F18" t="n">
-        <v>1.459</v>
+        <v>1.4548</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.6372</v>
+        <v>1.6784</v>
       </c>
       <c r="H18" t="n">
-        <v>0.5641</v>
+        <v>0.514</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.2012</v>
+        <v>1.1644</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1382</v>
+        <v>0.8426</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1785</v>
+        <v>0.6218</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.0403</v>
+        <v>0.2208</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.7754</v>
+        <v>0.8358</v>
       </c>
       <c r="N18" t="n">
-        <v>0.3856</v>
+        <v>-0.1078</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.1609</v>
+        <v>0.9436</v>
       </c>
       <c r="P18" t="n">
-        <v>2.5515</v>
+        <v>0.4639</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.232</v>
       </c>
       <c r="R18" t="n">
-        <v>2.5515</v>
+        <v>0.6959</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3519</v>
+        <v>-0.2891</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1766</v>
+        <v>-0.2122</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1753</v>
+        <v>-0.0769</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>O. DA SILVA</t>
+          <t>J. JESSUP</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.2585</v>
+        <v>1.7501</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1626</v>
+        <v>1.4727</v>
       </c>
       <c r="F19" t="n">
-        <v>1.0959</v>
+        <v>0.2773</v>
       </c>
       <c r="G19" t="n">
-        <v>1.6784</v>
+        <v>1.5323</v>
       </c>
       <c r="H19" t="n">
-        <v>0.514</v>
+        <v>-1.7969</v>
       </c>
       <c r="I19" t="n">
-        <v>1.1644</v>
+        <v>3.3292</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8426</v>
+        <v>2.1723</v>
       </c>
       <c r="K19" t="n">
-        <v>0.6218</v>
+        <v>-1.3206</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2208</v>
+        <v>3.493</v>
       </c>
       <c r="M19" t="n">
-        <v>0.8358</v>
+        <v>-0.64</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1078</v>
+        <v>-0.4762</v>
       </c>
       <c r="O19" t="n">
-        <v>0.9436</v>
+        <v>-0.1638</v>
       </c>
       <c r="P19" t="n">
-        <v>0.4639</v>
+        <v>1.1598</v>
       </c>
       <c r="Q19" t="n">
         <v>-0.232</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6959</v>
+        <v>1.3917</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8839</v>
+        <v>-0.8002</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4481</v>
+        <v>-0.4676</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4358</v>
+        <v>-0.3325</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. JESSUP</t>
+          <t>I. MIKE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.1946</v>
+        <v>1.7244</v>
       </c>
       <c r="E20" t="n">
-        <v>1.1189</v>
+        <v>-0.0384</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0757</v>
+        <v>1.7628</v>
       </c>
       <c r="G20" t="n">
-        <v>1.5323</v>
+        <v>-0.6372</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.7969</v>
+        <v>0.5641</v>
       </c>
       <c r="I20" t="n">
-        <v>3.3292</v>
+        <v>-1.2012</v>
       </c>
       <c r="J20" t="n">
-        <v>2.1723</v>
+        <v>0.1382</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.3206</v>
+        <v>0.1785</v>
       </c>
       <c r="L20" t="n">
-        <v>3.493</v>
+        <v>-0.0403</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.64</v>
+        <v>-0.7754</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4762</v>
+        <v>0.3856</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1638</v>
+        <v>-1.1609</v>
       </c>
       <c r="P20" t="n">
-        <v>1.1598</v>
+        <v>2.5515</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.232</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3917</v>
+        <v>2.5515</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.3557</v>
+        <v>-0.0481</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8215</v>
+        <v>-0.1766</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5342</v>
+        <v>0.1285</v>
       </c>
       <c r="V20" t="n">
         <v>-0.1418</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1992</v>
+        <v>0.9735</v>
       </c>
       <c r="E21" t="n">
         <v>-1.5176</v>
       </c>
       <c r="F21" t="n">
-        <v>1.7168</v>
+        <v>2.491</v>
       </c>
       <c r="G21" t="n">
         <v>-0.4388</v>
@@ -2092,13 +2092,13 @@
         <v>2.7834</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8439</v>
+        <v>-0.0696</v>
       </c>
       <c r="T21" t="n">
         <v>-0.1766</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6673</v>
+        <v>0.107</v>
       </c>
       <c r="V21" t="n">
         <v>-0.1418</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.3287</v>
+        <v>-0.9419</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.718</v>
+        <v>-2.1282</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3893</v>
+        <v>1.1864</v>
       </c>
       <c r="G22" t="n">
         <v>-0.4249</v>
@@ -2170,13 +2170,13 @@
         <v>2.7834</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.2233</v>
+        <v>-0.8364</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.1123</v>
+        <v>-0.5226</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.111</v>
+        <v>-0.3139</v>
       </c>
       <c r="V22" t="n">
         <v>-1.0722</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>W. GABRIEL</t>
+          <t>X. RATHAN-MAYES</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.1367</v>
+        <v>-2.9423</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.4724</v>
+        <v>-2.9892</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.6643</v>
+        <v>0.0469</v>
       </c>
       <c r="G23" t="n">
-        <v>1.7261</v>
+        <v>-1.3463</v>
       </c>
       <c r="H23" t="n">
-        <v>1.4081</v>
+        <v>-1.6038</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3179</v>
+        <v>0.2575</v>
       </c>
       <c r="J23" t="n">
-        <v>1.7405</v>
+        <v>-1.5426</v>
       </c>
       <c r="K23" t="n">
-        <v>1.6301</v>
+        <v>-1.5391</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1104</v>
+        <v>-0.0035</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.0144</v>
+        <v>0.1963</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.222</v>
+        <v>-0.06469999999999999</v>
       </c>
       <c r="O23" t="n">
-        <v>0.2075</v>
+        <v>0.261</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.7834</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.4793</v>
+        <v>-1.1598</v>
       </c>
       <c r="R23" t="n">
         <v>0.6959</v>
       </c>
       <c r="S23" t="n">
-        <v>0.9955000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="T23" t="n">
-        <v>1.1246</v>
+        <v>-0.2869</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1291</v>
+        <v>0.2269</v>
       </c>
       <c r="V23" t="n">
-        <v>-3.0748</v>
+        <v>-1.0722</v>
       </c>
       <c r="W23" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-3.2166</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X. RATHAN-MAYES</t>
+          <t>W. GABRIEL</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.4363</v>
+        <v>-4.0575</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.2251</v>
+        <v>-1.416</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.2112</v>
+        <v>-2.6415</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.3463</v>
+        <v>1.7261</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.6038</v>
+        <v>1.4081</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2575</v>
+        <v>0.3179</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.5426</v>
+        <v>1.7405</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.5391</v>
+        <v>1.6301</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.0035</v>
+        <v>0.1104</v>
       </c>
       <c r="M24" t="n">
-        <v>0.1963</v>
+        <v>-0.0144</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.06469999999999999</v>
+        <v>-0.222</v>
       </c>
       <c r="O24" t="n">
-        <v>0.261</v>
+        <v>0.2075</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.4639</v>
+        <v>-2.7834</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.1598</v>
+        <v>-3.4793</v>
       </c>
       <c r="R24" t="n">
         <v>0.6959</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.554</v>
+        <v>0.0747</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5228</v>
+        <v>0.181</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0312</v>
+        <v>-0.1063</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.0722</v>
+        <v>-3.0748</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.0722</v>
+        <v>-3.2166</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>5.141500000000002</v>
+        <v>8.286899999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.007599999999999163</v>
+        <v>-0.007600000000000939</v>
       </c>
       <c r="F25" t="n">
-        <v>5.149</v>
+        <v>8.2943</v>
       </c>
       <c r="G25" t="n">
         <v>10.9193</v>
@@ -2374,7 +2374,7 @@
         <v>6.452500000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>4.466900000000001</v>
+        <v>4.4669</v>
       </c>
       <c r="J25" t="n">
         <v>12.565</v>
@@ -2389,13 +2389,13 @@
         <v>-1.6459</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.2917000000000001</v>
+        <v>-0.2917</v>
       </c>
       <c r="O25" t="n">
         <v>-1.3542</v>
       </c>
       <c r="P25" t="n">
-        <v>3.479399999999999</v>
+        <v>3.4794</v>
       </c>
       <c r="Q25" t="n">
         <v>-13.9173</v>
@@ -2404,13 +2404,13 @@
         <v>17.3965</v>
       </c>
       <c r="S25" t="n">
-        <v>-5.5045</v>
+        <v>-2.359</v>
       </c>
       <c r="T25" t="n">
-        <v>-2.297700000000001</v>
+        <v>-2.2977</v>
       </c>
       <c r="U25" t="n">
-        <v>-3.2068</v>
+        <v>-0.06130000000000008</v>
       </c>
       <c r="V25" t="n">
         <v>-3.7527</v>
